--- a/it_forms/033_tech_ux_audit_form--it_forms.xlsx
+++ b/it_forms/033_tech_ux_audit_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>option 5</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_d</t>
+          <t>option d</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_e</t>
+          <t>option e</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_f</t>
+          <t>option f</t>
         </is>
       </c>
     </row>
